--- a/data/trans_dic/P40_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P40_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud bueno o muy bueno (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es buena o muy buena (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>50,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,65; 71,34</t>
+          <t>65,58; 71,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,79; 69,35</t>
+          <t>62,94; 69,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,39; 70,14</t>
+          <t>63,28; 70,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54,64; 62,72</t>
+          <t>56,95; 64,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,36; 55,87</t>
+          <t>50,24; 55,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,78; 55,43</t>
+          <t>49,8; 55,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,77; 55,24</t>
+          <t>48,49; 55,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,18; 45,86</t>
+          <t>40,9; 46,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,94; 62,01</t>
+          <t>58,0; 61,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56,05; 60,34</t>
+          <t>56,16; 60,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,14; 60,92</t>
+          <t>56,06; 60,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,2; 52,03</t>
+          <t>48,44; 53,02</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,64; 92,48</t>
+          <t>89,77; 92,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,94; 90,84</t>
+          <t>87,92; 90,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,49; 89,5</t>
+          <t>86,55; 89,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83,37; 90,21</t>
+          <t>83,11; 86,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,37; 84,14</t>
+          <t>80,46; 84,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,05; 85,68</t>
+          <t>82,27; 85,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,42; 83,94</t>
+          <t>80,43; 84,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,03; 83,38</t>
+          <t>77,33; 80,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>85,7; 88,05</t>
+          <t>85,55; 88,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85,63; 88,0</t>
+          <t>85,61; 87,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83,88; 86,24</t>
+          <t>83,96; 86,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,04; 85,22</t>
+          <t>80,67; 82,86</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,79%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,5; 93,5</t>
+          <t>88,38; 93,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,45; 94,3</t>
+          <t>88,82; 94,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,7; 93,7</t>
+          <t>88,89; 94,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,59; 89,92</t>
+          <t>85,19; 90,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,32; 88,49</t>
+          <t>81,93; 88,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,63; 93,71</t>
+          <t>87,84; 93,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,64; 92,24</t>
+          <t>86,46; 92,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,94; 88,44</t>
+          <t>83,25; 87,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,53; 90,51</t>
+          <t>86,49; 90,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89,4; 93,49</t>
+          <t>89,34; 93,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88,66; 92,22</t>
+          <t>88,65; 92,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85,18; 88,58</t>
+          <t>85,1; 88,35</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,67; 85,29</t>
+          <t>82,78; 85,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,66; 84,41</t>
+          <t>81,82; 84,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,6; 85,19</t>
+          <t>82,51; 85,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,15; 85,98</t>
+          <t>79,92; 82,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,85; 73,07</t>
+          <t>69,81; 72,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,43; 74,66</t>
+          <t>71,39; 74,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,12; 76,29</t>
+          <t>73,28; 76,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68,93; 76,69</t>
+          <t>71,24; 73,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76,63; 78,6</t>
+          <t>76,59; 78,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76,96; 78,96</t>
+          <t>76,92; 79,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78,27; 80,25</t>
+          <t>78,28; 80,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,96; 80,19</t>
+          <t>75,83; 77,72</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud bueno o muy bueno (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es buena o muy buena (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303649</t>
+          <t>352738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>325362</t>
+          <t>358212</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>629011</t>
+          <t>710950</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>676712; 735391</t>
+          <t>676028; 735355</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>606894; 670297</t>
+          <t>608329; 671559</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>472624; 522887</t>
+          <t>471804; 523435</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>281382; 322994</t>
+          <t>329464; 373472</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>661369; 733811</t>
+          <t>659845; 732693</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>664050; 739376</t>
+          <t>664289; 742460</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>482456; 546424</t>
+          <t>479665; 546431</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>303566; 346499</t>
+          <t>336191; 381185</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1358278; 1453504</t>
+          <t>1359589; 1447403</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1289360; 1388145</t>
+          <t>1291968; 1387700</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>973904; 1056761</t>
+          <t>972520; 1057297</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>599627; 660969</t>
+          <t>678473; 742614</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1962916</t>
+          <t>1884595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1757373</t>
+          <t>1714118</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3720289</t>
+          <t>3598714</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1516306; 1564314</t>
+          <t>1518462; 1565956</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1697767; 1753642</t>
+          <t>1697239; 1754068</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1787617; 1849870</t>
+          <t>1788924; 1848799</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1909343; 2066142</t>
+          <t>1853911; 1919610</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1276084; 1335919</t>
+          <t>1277505; 1339331</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1428471; 1491563</t>
+          <t>1432291; 1494146</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1583756; 1653067</t>
+          <t>1584066; 1654245</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1589626; 1865845</t>
+          <t>1679138; 1746201</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2810349; 2887380</t>
+          <t>2805235; 2887493</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3143725; 3231038</t>
+          <t>3143049; 3228531</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3385502; 3480979</t>
+          <t>3388932; 3480984</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3533675; 3859092</t>
+          <t>3551107; 3647608</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>566059</t>
+          <t>624821</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>570066</t>
+          <t>630547</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1136125</t>
+          <t>1255368</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>488007; 515549</t>
+          <t>487318; 515704</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>423064; 451084</t>
+          <t>424850; 451703</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>483393; 510641</t>
+          <t>484422; 512401</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>546994; 581419</t>
+          <t>606176; 642715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>392178; 421590</t>
+          <t>390325; 422694</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>399777; 427520</t>
+          <t>400729; 427202</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>470706; 501136</t>
+          <t>469734; 501206</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>554408; 584134</t>
+          <t>611785; 645662</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>889408; 930292</t>
+          <t>888952; 929992</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>835442; 873687</t>
+          <t>834906; 873180</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>964853; 1003531</t>
+          <t>964696; 1006340</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1113357; 1157878</t>
+          <t>1230960; 1278003</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2832624</t>
+          <t>2862155</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2652801</t>
+          <t>2702877</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5485426</t>
+          <t>5565032</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2706368; 2792019</t>
+          <t>2710132; 2790716</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2756483; 2849347</t>
+          <t>2761749; 2850343</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2773194; 2860294</t>
+          <t>2770229; 2859419</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2766640; 2967965</t>
+          <t>2813839; 2905852</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2359049; 2467710</t>
+          <t>2357868; 2465095</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2522214; 2636148</t>
+          <t>2520676; 2632262</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2560620; 2671541</t>
+          <t>2566025; 2674541</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2518634; 2802047</t>
+          <t>2655954; 2749057</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5096678; 5227843</t>
+          <t>5094118; 5234445</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5315160; 5453133</t>
+          <t>5312505; 5457302</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5368881; 5504575</t>
+          <t>5369713; 5511822</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5326231; 5697715</t>
+          <t>5496662; 5633876</t>
         </is>
       </c>
     </row>
